--- a/reports/gms_7_20260513.xlsx
+++ b/reports/gms_7_20260513.xlsx
@@ -525,503 +525,523 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⁠000035</t>
+          <t>⁠600285</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中国天楹</t>
+          <t>羚锐制药</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>左侧</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量30.0(推力40.0+支撑-10.0+攻击0.0)</t>
+          <t>总分75.0 蓄势75.0(引力20.0+平衡40.0+量缩15.0)A 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>⁠000533</t>
+          <t>⁠000709</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>河钢股份</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.98%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>总分55.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量55.0(推力40.0+支撑15.0+攻击0.0)</t>
+          <t>总分70.0 蓄势60.0(引力20.0+平衡40.0+量缩0.0) 动量70.0(推力40.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>⁠000558</t>
+          <t>⁠000905</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>天府文旅</t>
+          <t>厦门港务</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.11%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-11.97%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-10.69%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分70.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量70.0(推力40.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>⁠000572</t>
+          <t>⁠000533</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>海马汽车</t>
+          <t>顺钠股份</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.54%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-3.51%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>9.98%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>总分10.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量10.0(推力0.0+支撑-10.0+攻击20.0)</t>
+          <t>总分55.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量55.0(推力40.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>⁠000651</t>
+          <t>⁠301309</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>格力电器</t>
+          <t>万得凯</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.30</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.82%</t>
+          <t>-4.12%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>-4.04%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>-3.89%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>⁠000709</t>
+          <t>⁠601138</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>河钢股份</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>70.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15.82</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>25.22%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>22.33%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>28.75%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势60.0(引力20.0+平衡40.0+量缩0.0) 动量70.0(推力40.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>⁠000721</t>
+          <t>⁠603667</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>西安饮食</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>81.40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>70.50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>19.56%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-6.96%</t>
+          <t>16.94%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>20.40%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>⁠000905</t>
+          <t>⁠603979</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>厦门港务</t>
+          <t>金诚信</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>69.52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1032,22 +1052,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>63.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>12.45%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>11.39%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>12.86%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1057,568 +1077,573 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量70.0(推力40.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>⁠000983</t>
+          <t>⁠688066</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>山西焦煤</t>
+          <t>航天宏图</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>17.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>-24.61%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>-29.09%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>-22.53%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>⁠002050</t>
+          <t>⁠688981</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>51.50</t>
+          <t>121.86</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>110.60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16.59%</t>
+          <t>20.02%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.99%</t>
+          <t>18.17%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>17.63%</t>
+          <t>22.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>⁠002100</t>
+          <t>⁠300705</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天康生物</t>
+          <t>九典制药</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.24%</t>
+          <t>-10.58%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-11.18%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-10.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分45.0 蓄势45.0(引力30.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>⁠002155</t>
+          <t>⁠000035</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>湖南黄金</t>
+          <t>中国天楹</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
         <v>9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-6.97%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-6.70%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量30.0(推力40.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>⁠002171</t>
+          <t>⁠601628</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>楚江新材</t>
+          <t>中国人寿</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>36.48</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
-        <v>12</v>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6.70%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6.98%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分40.0 蓄势40.0(引力20.0+平衡20.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>⁠002202</t>
+          <t>⁠000721</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>西安饮食</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27.80</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15.21%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14.24%</t>
+          <t>-6.96%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16.61%</t>
+          <t>-6.51%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>⁠002230</t>
+          <t>⁠603588</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>高能环境</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.40</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>48.73</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>-23.34%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>-24.41%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.64%</t>
+          <t>-19.62%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>⁠002271</t>
+          <t>⁠000651</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>东方雨虹</t>
+          <t>格力电器</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>40.30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
         <v>11</v>
       </c>
-      <c r="H17" t="n">
-        <v>9</v>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>7.39%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>7.98%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-8.35%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力0.0+平衡20.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>⁠002364</t>
+          <t>⁠000983</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中恒电气</t>
+          <t>山西焦煤</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1628,48 +1653,48 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>39.13%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>34.03%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>51.58%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1681,148 +1706,148 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>⁠002430</t>
+          <t>⁠002050</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>杭氧股份</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>51.50</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>46.54</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>16.59%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>14.99%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>17.63%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>⁠002487</t>
+          <t>⁠002171</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>楚江新材</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.01</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>83.45</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.37%</t>
+          <t>6.70%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>12.43%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14.20%</t>
+          <t>6.98%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>⁠002506</t>
+          <t>⁠002202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>协鑫集成</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1832,80 +1857,80 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>27.80</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>15.21%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>14.24%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>16.61%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势20.0(引力0.0+平衡20.0+量缩0.0) 动量30.0(推力40.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>⁠002557</t>
+          <t>⁠002230</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>洽洽食品</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>49.40</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1916,22 +1941,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>48.73</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1941,24 +1966,24 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力0.0+平衡20.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>⁠002709</t>
+          <t>⁠002364</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>中恒电气</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1968,12 +1993,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>16.47</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1984,22 +2009,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.47%</t>
+          <t>39.13%</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24.22%</t>
+          <t>34.03%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>31.97%</t>
+          <t>51.58%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2009,24 +2034,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>⁠002715</t>
+          <t>⁠002506</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>登云股份</t>
+          <t>协鑫集成</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2036,692 +2061,677 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18.39%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16.90%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20.34%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势20.0(引力0.0+平衡20.0+量缩0.0) 动量30.0(推力40.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>⁠00700</t>
+          <t>⁠002709</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>497.35</t>
+          <t>57.92</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-35.60</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>497.35</t>
+          <t>53.01</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-7.16%</t>
+          <t>26.47%</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-7.46%</t>
+          <t>24.22%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-6.94%</t>
+          <t>31.97%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量10.0(推力0.0+支撑-10.0+攻击20.0)</t>
+          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>⁠00981</t>
+          <t>⁠002715</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>登云股份</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>58.70</t>
+          <t>17.51</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>58.70</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28.96%</t>
+          <t>18.39%</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>22.15%</t>
+          <t>16.90%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>28.45%</t>
+          <t>20.34%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>总分60.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量60.0(推力0.0+支撑30.0+攻击30.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>⁠01810</t>
+          <t>⁠300058</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>小米集团-W</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-16.31%</t>
+          <t>12.21%</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-16.71%</t>
+          <t>11.57%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-14.32%</t>
+          <t>13.09%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>⁠02269</t>
+          <t>⁠300223</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>药明生物</t>
+          <t>北京君正</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>148.65</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>123.72</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-2.46%</t>
+          <t>31.65%</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>26.34%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-2.46%</t>
+          <t>35.77%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>⁠02565</t>
+          <t>⁠300251</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>派格生物医药-B</t>
+          <t>光线传媒</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-30.27</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-66.08%</t>
+          <t>-9.95%</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-118.33%</t>
+          <t>-10.63%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-54.20%</t>
+          <t>-9.61%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>⁠02899</t>
+          <t>⁠300308</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>1049.20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>356.18</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>848.97</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9.65%</t>
+          <t>41.95%</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>9.07%</t>
+          <t>33.95%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>51.40%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>⁠03690</t>
+          <t>⁠300699</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>美团-W</t>
+          <t>光威复材</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.81</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>83.81</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>5.07%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>5.34%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>⁠03750</t>
+          <t>⁠300919</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中伟新材</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>45.0%</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>656.20</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>656.20</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>16.68%</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>16.07%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>19.14%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>总分45.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量45.0(推力0.0+支撑15.0+攻击30.0)</t>
+          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>⁠09988</t>
+          <t>⁠301275</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>阿里巴巴-W</t>
+          <t>汉朔科技</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>126.80</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>126.80</t>
+          <t>42.84</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>10.57%</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>9.74%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>6.74%</t>
+          <t>10.79%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.98%</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量35.0(推力0.0+支撑15.0+攻击20.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>⁠300058</t>
+          <t>⁠600105</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2731,48 +2741,48 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>17.19</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>12.21%</t>
+          <t>39.29%</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11.57%</t>
+          <t>33.17%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>13.09%</t>
+          <t>49.62%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2784,80 +2794,80 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>⁠300139</t>
+          <t>⁠600196</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>晓程科技</t>
+          <t>复星医药</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-4.77%</t>
+          <t>-6.19%</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>-6.37%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-4.63%</t>
+          <t>-5.99%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力30.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>⁠300223</t>
+          <t>⁠600570</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>北京君正</t>
+          <t>恒生电子</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2867,48 +2877,48 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>148.65</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>123.72</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>31.65%</t>
+          <t>5.16%</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>26.34%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>35.77%</t>
+          <t>5.31%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2920,12 +2930,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>⁠300251</t>
+          <t>⁠601231</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>光线传媒</t>
+          <t>环旭电子</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2935,12 +2945,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2951,22 +2961,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-9.95%</t>
+          <t>19.43%</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-10.63%</t>
+          <t>17.48%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-9.61%</t>
+          <t>21.18%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2976,24 +2986,24 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>⁠300308</t>
+          <t>⁠601636</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>旗滨集团</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3003,48 +3013,48 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1049.20</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>356.18</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H38" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>848.97</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41.95%</t>
+          <t>15.92%</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>33.95%</t>
+          <t>14.60%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>51.40%</t>
+          <t>17.10%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3056,12 +3066,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>⁠300699</t>
+          <t>⁠603103</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>光威复材</t>
+          <t>横店影视</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3071,201 +3081,201 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>-8.32%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>-7.68%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>⁠300705</t>
+          <t>⁠603933</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>九典制药</t>
+          <t>睿能科技</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>26.29</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-10.58%</t>
+          <t>16.56%</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-11.18%</t>
+          <t>15.18%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-10.06%</t>
+          <t>17.89%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>总分45.0 蓄势45.0(引力30.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>⁠300750</t>
+          <t>⁠688025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>434.05</t>
+          <t>369.00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>93.40</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>435.74</t>
+          <t>312.13</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10.11%</t>
+          <t>29.92%</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10.15%</t>
+          <t>25.31%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>11.30%</t>
+          <t>33.89%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>⁠300919</t>
+          <t>⁠688027</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中伟新材</t>
+          <t>国盾量子</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3275,133 +3285,133 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>609.97</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>576.11</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>16.68%</t>
+          <t>11.04%</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16.07%</t>
+          <t>10.43%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>19.14%</t>
+          <t>11.64%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>⁠300994</t>
+          <t>⁠688028</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>久祺股份</t>
+          <t>沃尔德</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>139.05</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>112.66</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-3.24%</t>
+          <t>34.84%</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>28.23%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>39.33%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>⁠301275</t>
+          <t>⁠688114</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>汉朔科技</t>
+          <t>华大智造</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3411,48 +3421,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>51.65</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>42.84</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>10.57%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>9.74%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>10.79%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3464,80 +3474,80 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>⁠301309</t>
+          <t>⁠688291</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>万得凯</t>
+          <t>金橙子</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" t="n">
         <v>14</v>
       </c>
-      <c r="H45" t="n">
-        <v>6</v>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>43.98</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-4.12%</t>
+          <t>18.12%</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-4.04%</t>
+          <t>16.65%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-3.89%</t>
+          <t>19.98%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>⁠600105</t>
+          <t>⁠688498</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>源杰科技</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3547,12 +3557,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>1708.00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17.19</t>
+          <t>579.82</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3563,22 +3573,22 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>1425.25</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>39.29%</t>
+          <t>40.68%</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>33.17%</t>
+          <t>33.95%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>49.62%</t>
+          <t>51.39%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3588,24 +3598,24 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>⁠600196</t>
+          <t>⁠688795</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>复星医药</t>
+          <t>摩尔线程-U</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3615,138 +3625,133 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>718.07</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>128.05</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>25.70</t>
+          <t>657.82</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-6.19%</t>
+          <t>19.47%</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-6.37%</t>
+          <t>17.83%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-5.99%</t>
+          <t>21.70%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力30.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>⁠600285</t>
+          <t>⁠000558</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>羚锐制药</t>
+          <t>天府文旅</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>左侧</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
         <v>6</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-11.11%</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-11.97%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-10.69%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>总分75.0 蓄势75.0(引力20.0+平衡40.0+量缩15.0)A 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>⁠600307</t>
+          <t>⁠002100</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>天康生物</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3756,48 +3761,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-7.22%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>-7.39%</t>
+          <t>-5.61%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-6.88%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3809,12 +3814,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>⁠600525</t>
+          <t>⁠002271</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>东方雨虹</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3824,133 +3829,133 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>-8.35%</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力0.0+平衡20.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>⁠600570</t>
+          <t>⁠002557</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>恒生电子</t>
+          <t>洽洽食品</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力0.0+平衡20.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>⁠600838</t>
+          <t>⁠300139</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>晓程科技</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3960,48 +3965,48 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>13</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>56.36</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-9.68%</t>
+          <t>-4.77%</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-10.37%</t>
+          <t>-4.86%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-9.40%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4013,1528 +4018,1523 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>⁠600875</t>
+          <t>⁠600307</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>东方电气</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>-7.22%</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>-7.39%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>6.63%</t>
+          <t>-6.88%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.10%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>总分15.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>⁠600966</t>
+          <t>⁠600525</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>博汇纸业</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>-6.85%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-6.41%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>⁠601138</t>
+          <t>⁠600838</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>70.84</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>25.22%</t>
+          <t>-9.68%</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>22.33%</t>
+          <t>-10.37%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>28.75%</t>
+          <t>-9.40%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>⁠601231</t>
+          <t>⁠002430</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>环旭电子</t>
+          <t>杭氧股份</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>30.20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>19.43%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>17.48%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>21.18%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分15.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>⁠601628</t>
+          <t>⁠002487</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中国人寿</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>83.01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>83.45</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>12.37%</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>12.43%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>14.20%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>总分40.0 蓄势40.0(引力20.0+平衡20.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>⁠601636</t>
+          <t>⁠300750</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>旗滨集团</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>434.05</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>435.74</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>15.92%</t>
+          <t>10.11%</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>14.60%</t>
+          <t>10.15%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>17.10%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>⁠603103</t>
+          <t>⁠300994</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>横店影视</t>
+          <t>久祺股份</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-7.82%</t>
+          <t>-3.24%</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>-8.32%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-7.68%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>⁠603583</t>
+          <t>⁠600875</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>捷昌驱动</t>
+          <t>东方电气</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" t="n">
         <v>11</v>
       </c>
-      <c r="H60" t="n">
-        <v>9</v>
-      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-13.69%</t>
+          <t>6.29%</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>-15.20%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-13.20%</t>
+          <t>6.63%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>6.10%</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>⁠603588</t>
+          <t>⁠000572</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>高能环境</t>
+          <t>海马汽车</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-23.34%</t>
+          <t>-3.54%</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-24.41%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-19.62%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分10.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量10.0(推力0.0+支撑-10.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>⁠603667</t>
+          <t>⁠002155</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>湖南黄金</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>81.40</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="G62" t="n">
+        <v>11</v>
+      </c>
+      <c r="H62" t="n">
         <v>9</v>
       </c>
-      <c r="H62" t="n">
-        <v>11</v>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>70.50</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19.56%</t>
+          <t>-6.97%</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>16.94%</t>
+          <t>-7.18%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>20.40%</t>
+          <t>-6.70%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>⁠603933</t>
+          <t>⁠600966</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>博汇纸业</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>16.56%</t>
+          <t>-6.52%</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15.18%</t>
+          <t>-6.85%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>17.89%</t>
+          <t>-6.41%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>⁠603979</t>
+          <t>⁠603583</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>金诚信</t>
+          <t>捷昌驱动</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>12.45%</t>
+          <t>-13.69%</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>11.39%</t>
+          <t>-15.20%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>12.86%</t>
+          <t>-13.20%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>⁠688025</t>
+          <t>⁠688256</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>寒武纪-U</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>369.00</t>
+          <t>1316.88</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>93.40</t>
+          <t>118.88</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>312.13</t>
+          <t>1356.21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>29.92%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>25.31%</t>
+          <t>9.03%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>33.89%</t>
+          <t>9.92%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>⁠688027</t>
+          <t>⁠920263</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>国盾量子</t>
+          <t>中航泰达</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>609.97</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="G66" t="n">
+        <v>11</v>
+      </c>
+      <c r="H66" t="n">
         <v>9</v>
       </c>
-      <c r="H66" t="n">
-        <v>11</v>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>576.11</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>11.04%</t>
+          <t>-14.23%</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>10.43%</t>
+          <t>-16.06%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>11.64%</t>
+          <t>-13.84%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>⁠688028</t>
+          <t>⁠00981</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>沃尔德</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>139.05</t>
+          <t>58.70</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H67" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>112.66</t>
+          <t>58.70</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>34.84%</t>
+          <t>28.96%</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28.23%</t>
+          <t>22.15%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>39.33%</t>
+          <t>28.45%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分60.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量60.0(推力0.0+支撑30.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>⁠688066</t>
+          <t>⁠02565</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>航天宏图</t>
+          <t>派格生物医药-B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-30.27</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-24.61%</t>
+          <t>-66.08%</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>-29.09%</t>
+          <t>-118.33%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-22.53%</t>
+          <t>-54.20%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>⁠688114</t>
+          <t>⁠03750</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>华大智造</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>51.65</t>
+          <t>656.20</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>656.20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分45.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量45.0(推力0.0+支撑15.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>⁠688256</t>
+          <t>⁠09988</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>寒武纪-U</t>
+          <t>阿里巴巴-W</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1316.88</t>
+          <t>126.80</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>118.88</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H70" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1356.21</t>
+          <t>126.80</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>9.03%</t>
+          <t>6.32%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>9.92%</t>
+          <t>6.74%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量35.0(推力0.0+支撑15.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>⁠688291</t>
+          <t>⁠00700</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>金橙子</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>497.34</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>-35.60</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H71" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>43.98</t>
+          <t>497.34</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>18.12%</t>
+          <t>-7.16%</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>16.65%</t>
+          <t>-7.46%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>19.98%</t>
+          <t>-6.94%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量10.0(推力0.0+支撑-10.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>⁠688498</t>
+          <t>⁠01810</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>源杰科技</t>
+          <t>小米集团-W</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1708.00</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>579.82</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1425.25</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>40.68%</t>
+          <t>-16.31%</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>33.95%</t>
+          <t>-16.71%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>51.39%</t>
+          <t>-14.32%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>⁠688795</t>
+          <t>⁠03690</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>摩尔线程-U</t>
+          <t>美团-W</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>718.07</t>
+          <t>83.81</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>128.05</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="G73" t="n">
+        <v>13</v>
+      </c>
+      <c r="H73" t="n">
         <v>7</v>
       </c>
-      <c r="H73" t="n">
-        <v>13</v>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>657.82</t>
+          <t>83.81</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>19.47%</t>
+          <t>4.24%</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17.83%</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>21.70%</t>
+          <t>4.40%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>⁠688981</t>
+          <t>⁠02899</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>右侧</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>121.86</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H74" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>110.60</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>20.02%</t>
+          <t>9.65%</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18.17%</t>
+          <t>9.07%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>22.20%</t>
+          <t>9.97%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
+          <t>总分15.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>⁠920263</t>
+          <t>⁠02269</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>中航泰达</t>
+          <t>药明生物</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5544,48 +5544,48 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-14.23%</t>
+          <t>-2.46%</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-16.06%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-13.84%</t>
+          <t>-2.46%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
